--- a/Unified_PDF_Platform/unified_outputs/APL- Rapid Trading- Dec 25_invoice.xlsx
+++ b/Unified_PDF_Platform/unified_outputs/APL- Rapid Trading- Dec 25_invoice.xlsx
@@ -963,23 +963,15 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>INVOICE TOTAL</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>GRAND TOTAL</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>

--- a/Unified_PDF_Platform/unified_outputs/APL- Rapid Trading- Dec 25_invoice.xlsx
+++ b/Unified_PDF_Platform/unified_outputs/APL- Rapid Trading- Dec 25_invoice.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -547,7 +547,11 @@
           <t>1560</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MEDLINK9 GROUP MED SUP</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>2480131</t>
@@ -584,7 +588,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -603,7 +607,11 @@
           <t>8855</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MEDLINK9 GROUP MED SUP</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>2480128</t>
@@ -640,7 +648,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -659,7 +667,11 @@
           <t>1486</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MEDLINK9 GROUP MED SUP</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>2480132</t>
@@ -696,7 +708,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -715,7 +727,11 @@
           <t>4279</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MEDLINK9 GROUP MED SUP</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>2480130</t>
@@ -752,7 +768,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -771,7 +787,11 @@
           <t>9511</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MEDLINK9 GROUP MED SUP</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>2480129</t>
@@ -808,7 +828,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -827,7 +847,11 @@
           <t>5214</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MEDLINK9 GROUP MED SUP</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>2480127</t>
@@ -864,7 +888,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -883,7 +907,11 @@
           <t>0016</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MEDLINK9 GROUP MED SUP</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>2559492</t>
@@ -920,7 +948,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -939,7 +967,11 @@
           <t>3439</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MEDLINK9 GROUP MED SUP</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>2480133</t>

--- a/Unified_PDF_Platform/unified_outputs/APL- Rapid Trading- Dec 25_invoice.xlsx
+++ b/Unified_PDF_Platform/unified_outputs/APL- Rapid Trading- Dec 25_invoice.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -528,7 +528,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -547,22 +547,22 @@
           <t>1560</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2480131</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>MEDLINK9 GROUP MED SUP</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2480131</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>MEDLINK9 GROUP MED SUP</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>61.34</v>
@@ -588,7 +588,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -607,22 +607,22 @@
           <t>8855</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2480128</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>MEDLINK9 GROUP MED SUP</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2480128</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>MEDLINK9 GROUP MED SUP</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>128.93</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -667,22 +667,22 @@
           <t>1486</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2480132</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>MEDLINK9 GROUP MED SUP</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2480132</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>MEDLINK9 GROUP MED SUP</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>101.85</v>
@@ -708,7 +708,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,22 +727,22 @@
           <t>4279</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2480130</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>MEDLINK9 GROUP MED SUP</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2480130</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>MEDLINK9 GROUP MED SUP</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>61.34</v>
@@ -768,7 +768,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -787,22 +787,22 @@
           <t>9511</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2480129</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>MEDLINK9 GROUP MED SUP</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2480129</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>MEDLINK9 GROUP MED SUP</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
         <v>61.34</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -847,22 +847,22 @@
           <t>5214</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2480127</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>MEDLINK9 GROUP MED SUP</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2480127</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>MEDLINK9 GROUP MED SUP</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>128.93</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -907,22 +907,22 @@
           <t>0016</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2559492</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>MEDLINK9 GROUP MED SUP</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2559492</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>MEDLINK9 GROUP MED SUP</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
         <v>61.34</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -967,22 +967,22 @@
           <t>3439</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2480133</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>MEDLINK9 GROUP MED SUP</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2480133</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>MEDLINK9 GROUP MED SUP</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
         <v>61.34</v>

--- a/Unified_PDF_Platform/unified_outputs/APL- Rapid Trading- Dec 25_invoice.xlsx
+++ b/Unified_PDF_Platform/unified_outputs/APL- Rapid Trading- Dec 25_invoice.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,11 +504,6 @@
           <t>ADJUSTMENT_PREMIUM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>PRICING_ADJUSTMENT</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -528,7 +523,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -547,7 +542,11 @@
           <t>1560</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2480131</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>2480131</t>
@@ -563,12 +562,15 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N2" t="n">
         <v>61.34</v>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -607,7 +609,11 @@
           <t>8855</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2480128</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>2480128</t>
@@ -623,12 +629,15 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N3" t="n">
         <v>128.93</v>
       </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -648,7 +657,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -667,7 +676,11 @@
           <t>1486</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2480132</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>2480132</t>
@@ -683,12 +696,15 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N4" t="n">
         <v>101.85</v>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -708,7 +724,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,7 +743,11 @@
           <t>4279</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2480130</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>2480130</t>
@@ -743,12 +763,15 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N5" t="n">
         <v>61.34</v>
       </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -768,7 +791,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -787,7 +810,11 @@
           <t>9511</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2480129</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>2480129</t>
@@ -803,12 +830,15 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N6" t="n">
         <v>61.34</v>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -828,7 +858,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -847,7 +877,11 @@
           <t>5214</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2480127</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>2480127</t>
@@ -863,12 +897,15 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N7" t="n">
         <v>128.93</v>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -888,7 +925,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -907,7 +944,11 @@
           <t>0016</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2559492</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>2559492</t>
@@ -923,12 +964,15 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N8" t="n">
         <v>61.34</v>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -948,7 +992,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -967,7 +1011,11 @@
           <t>3439</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2480133</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>2480133</t>
@@ -983,12 +1031,15 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N9" t="n">
         <v>61.34</v>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1003,16 +1054,38 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>GRAND TOTAL</t>
+          <t>TOTAL CURRENT PREMIUM</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>666.41</v>
+        <v>666.4100000000001</v>
       </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL (COMBINED)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>666.4100000000001</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
